--- a/outputs/QLD_negative_prices.xlsx
+++ b/outputs/QLD_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3372,40 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3383,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6306,8 +6340,42 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B85">
+  <conditionalFormatting sqref="B2:B86">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6319,7 +6387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C85">
+  <conditionalFormatting sqref="C2:C86">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6331,7 +6399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D85">
+  <conditionalFormatting sqref="D2:D86">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6343,7 +6411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E85">
+  <conditionalFormatting sqref="E2:E86">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,7 +6423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F85">
+  <conditionalFormatting sqref="F2:F86">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6367,7 +6435,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G85">
+  <conditionalFormatting sqref="G2:G86">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6379,7 +6447,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H85">
+  <conditionalFormatting sqref="H2:H86">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6391,7 +6459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I85">
+  <conditionalFormatting sqref="I2:I86">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6403,7 +6471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J85">
+  <conditionalFormatting sqref="J2:J86">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6425,7 +6493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9606,6 +9674,43 @@
         <v>2</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>2976</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>555</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/QLD_negative_prices.xlsx
+++ b/outputs/QLD_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3406,6 +3406,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3417,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,8 +6408,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B86">
+  <conditionalFormatting sqref="B2:B87">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6387,7 +6455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C86">
+  <conditionalFormatting sqref="C2:C87">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6399,7 +6467,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D86">
+  <conditionalFormatting sqref="D2:D87">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6411,7 +6479,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E86">
+  <conditionalFormatting sqref="E2:E87">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6423,7 +6491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F86">
+  <conditionalFormatting sqref="F2:F87">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6435,7 +6503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G86">
+  <conditionalFormatting sqref="G2:G87">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6447,7 +6515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H86">
+  <conditionalFormatting sqref="H2:H87">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6459,7 +6527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I86">
+  <conditionalFormatting sqref="I2:I87">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6471,7 +6539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J86">
+  <conditionalFormatting sqref="J2:J87">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6493,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9711,6 +9779,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/QLD_negative_prices.xlsx
+++ b/outputs/QLD_negative_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.1</v>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1.04</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6.55</v>
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>16.53</v>
+        <v>15.97</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>13.47</v>
+        <v>13.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13.19</v>
+        <v>13.02</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6.98</v>
+        <v>6.91</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.49</v>
+        <v>6.42</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.46</v>
+        <v>6.39</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>2.95</v>
@@ -693,31 +693,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6.75</v>
+        <v>6.45</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.95</v>
+        <v>5.78</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5.54</v>
+        <v>5.38</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -798,28 +798,28 @@
         <v>0.3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
@@ -863,28 +863,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.1</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1.22</v>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>13.81</v>
+        <v>13.51</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9.68</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>7.86</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>3.97</v>
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>24.83</v>
+        <v>24.7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>21.4</v>
+        <v>21.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>20.46</v>
+        <v>20.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>16.97</v>
+        <v>16.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7.96</v>
+        <v>7.93</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>3.83</v>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>24.65</v>
+        <v>24.24</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>22.33</v>
+        <v>22.15</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20.56</v>
+        <v>20.45</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15.83</v>
+        <v>15.73</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>4.97</v>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16.94</v>
+        <v>16.7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13.37</v>
+        <v>13.24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12.43</v>
+        <v>12.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11.02</v>
+        <v>10.85</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>4.03</v>
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.03</v>
+        <v>4.79</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.28</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1.21</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>13.12</v>
+        <v>12.4</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>8.58</v>
@@ -1314,22 +1314,22 @@
         <v>7.5</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>16.1</v>
+        <v>15.62</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12.57</v>
+        <v>12.37</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>11.63</v>
+        <v>11.42</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.71</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.12</v>
+        <v>7.01</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>5.14</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H27" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="J27" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -1407,28 +1407,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>7.09</v>
+        <v>7.06</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.71</v>
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>16.1</v>
+        <v>16.03</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.94</v>
+        <v>13.84</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.96</v>
+        <v>11.9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>2.62</v>
@@ -1475,31 +1475,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>44.41</v>
+        <v>43.82</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>33.61</v>
+        <v>33.33</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>30.35</v>
+        <v>30.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>26.7</v>
+        <v>26.53</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>11.04</v>
+        <v>10.97</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31">
@@ -1509,28 +1509,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>36.66</v>
+        <v>36.32</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>31.69</v>
+        <v>31.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30.88</v>
+        <v>30.68</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>28.19</v>
+        <v>27.99</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12.1</v>
+        <v>12.03</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>1.81</v>
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>16.49</v>
+        <v>16.25</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>13.47</v>
+        <v>13.23</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>13.23</v>
+        <v>12.99</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12.47</v>
+        <v>12.22</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>7.05</v>
+        <v>6.88</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>2.78</v>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1.95</v>
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1.75</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.63</v>
+        <v>6.39</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>3.26</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>4.94</v>
+        <v>4.23</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2.52</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>30.65</v>
+        <v>30.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.05</v>
+        <v>26.98</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>24.53</v>
+        <v>24.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22.65</v>
+        <v>22.61</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.86</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>10.42</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>28.4</v>
+        <v>28.09</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>24.03</v>
+        <v>23.92</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>21.81</v>
+        <v>21.77</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>20.28</v>
+        <v>20.24</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>17.64</v>
@@ -1917,19 +1917,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>12.97</v>
+        <v>12.87</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>9.74</v>
+        <v>9.68</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>7.63</v>
+        <v>7.56</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>5.01</v>
@@ -1951,25 +1951,25 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24.03</v>
+        <v>23.68</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>16.84</v>
+        <v>16.6</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>15</v>
+        <v>14.76</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>13.47</v>
+        <v>13.26</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.35</v>
@@ -1985,22 +1985,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>37.47</v>
+        <v>37.03</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>24.4</v>
+        <v>23.99</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>16.36</v>
+        <v>16.16</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.54</v>
+        <v>13.37</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.59</v>
+        <v>7.46</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>2.42</v>
@@ -2019,22 +2019,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>9.98</v>
+        <v>9.81</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>7.12</v>
+        <v>6.99</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>5.24</v>
+        <v>5.14</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.44</v>
@@ -2053,19 +2053,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>9.49</v>
+        <v>9.41</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>6.55</v>
+        <v>6.51</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.82</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.39</v>
+        <v>15.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.62</v>
+        <v>10.58</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.06</v>
+        <v>7.02</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>27.05</v>
+        <v>26.84</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>23.47</v>
+        <v>23.44</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>20.9</v>
+        <v>20.87</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>16.49</v>
+        <v>16.42</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>3.72</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>24.7</v>
+        <v>24.53</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>15.42</v>
+        <v>15.39</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>9.140000000000001</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>18.4</v>
+        <v>18.19</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>15.03</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.75</v>
+        <v>35.55</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>30.71</v>
@@ -2257,19 +2257,19 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>67.78</v>
+        <v>67.37</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>62.03</v>
+        <v>61.79</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>59.78</v>
+        <v>59.64</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>47.82</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>39.75</v>
+        <v>39.78</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>4.67</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>79.86</v>
+        <v>79.31</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>73.84999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>71.98</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46.7</v>
+        <v>46.49</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46.25</v>
+        <v>46.04</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>10.69</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>81.45</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>75.84</v>
+        <v>75.13</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>71.81</v>
+        <v>71.17</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>47.08</v>
+        <v>46.67</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>7.63</v>
@@ -2346,7 +2346,7 @@
         <v>0.37</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="J55" s="3" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>37.78</v>
+        <v>37.53</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>30.52</v>
+        <v>30.31</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>28.02</v>
+        <v>27.85</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>34.38</v>
+        <v>34.07</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>27.45</v>
+        <v>27.18</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>24.73</v>
+        <v>24.46</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>12.87</v>
+        <v>12.77</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>9.27</v>
@@ -2427,19 +2427,19 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>8.4</v>
+        <v>8.27</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>12.75</v>
+        <v>12.61</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.97</v>
+        <v>7.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0.65</v>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>21.34</v>
+        <v>21.14</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>16.1</v>
+        <v>15.96</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>13.58</v>
+        <v>13.44</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>2.02</v>
@@ -2529,16 +2529,16 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>33.06</v>
+        <v>32.74</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>30.21</v>
+        <v>29.93</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>26.25</v>
+        <v>26.11</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>7.22</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>42.88</v>
+        <v>42.57</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>33.67</v>
+        <v>33.53</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>23.02</v>
+        <v>22.92</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>17.78</v>
+        <v>17.71</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>3.73</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>33.5</v>
+        <v>33.53</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>30.31</v>
+        <v>30.38</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>19.49</v>
@@ -2665,19 +2665,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>51.28</v>
+        <v>50.91</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>47.88</v>
+        <v>47.51</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>38.17</v>
+        <v>38.1</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>35.22</v>
+        <v>35.15</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.51</v>
+        <v>21.47</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>4.3</v>
@@ -2699,19 +2699,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>83.68000000000001</v>
+        <v>83.16</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>81.67</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>76.84</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>73.23</v>
+        <v>72.92</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.37</v>
+        <v>54.24</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>4.2</v>
@@ -2733,19 +2733,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>77.52</v>
+        <v>76.88</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>76.31</v>
+        <v>75.67</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>71.27</v>
+        <v>70.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>37.74</v>
+        <v>37.43</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>1.98</v>
@@ -2767,19 +2767,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>38.19</v>
+        <v>38.06</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>37.26</v>
+        <v>37.15</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>33.23</v>
+        <v>33.19</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>27.05</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>36.83</v>
+        <v>36.59</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>35.62</v>
+        <v>35.38</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>27.79</v>
+        <v>27.59</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>2.28</v>
@@ -2835,16 +2835,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>47.58</v>
+        <v>47.21</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>46.54</v>
+        <v>46.2</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>44.89</v>
+        <v>44.56</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>30.38</v>
+        <v>30.21</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0.1</v>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>47.02</v>
+        <v>46.43</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>46.06</v>
+        <v>45.68</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>43.3</v>
+        <v>43.01</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>15.77</v>
+        <v>15.74</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>1.15</v>
@@ -2903,16 +2903,16 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>35.75</v>
+        <v>35.28</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>31.05</v>
+        <v>30.75</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>45.35</v>
+        <v>44.58</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>41.18</v>
+        <v>40.8</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.94</v>
+        <v>31.87</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>2.99</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>25.2</v>
+        <v>24.87</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>22.65</v>
+        <v>22.58</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>9.880000000000001</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>33.96</v>
+        <v>33.72</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>31.46</v>
+        <v>31.39</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>14.24</v>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>43.85</v>
+        <v>43.75</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>11.53</v>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>70.5</v>
+        <v>70.13</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>26.81</v>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>88.65000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>33.54</v>
+        <v>33.51</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>17.92</v>
+        <v>17.88</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>3.78</v>
@@ -3141,16 +3141,16 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>77.89</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.26000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>1.92</v>
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>71.84</v>
+        <v>71.08</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>55.52</v>
+        <v>55.07</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>4.06</v>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>59.58</v>
+        <v>57.73</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>25.74</v>
+        <v>25.4</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>3.49</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>25.3</v>
+        <v>21.37</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0.1</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>19.64</v>
+        <v>19.12</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>1.53</v>
@@ -3311,13 +3311,13 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>24.23</v>
+        <v>23.86</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>2.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>39.06</v>
+        <v>38.61</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>1.98</v>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.65</v>
+        <v>18.48</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0.17</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.48</v>
+        <v>22.38</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>34.27</v>
+        <v>34.04</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0.84</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.1</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1.04</v>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6.55</v>
@@ -3729,28 +3729,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>16.53</v>
+        <v>15.97</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>13.47</v>
+        <v>13.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13.19</v>
+        <v>13.02</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6.98</v>
+        <v>6.91</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.49</v>
+        <v>6.42</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.46</v>
+        <v>6.39</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>2.95</v>
@@ -3763,31 +3763,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6.75</v>
+        <v>6.45</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.95</v>
+        <v>5.78</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5.54</v>
+        <v>5.38</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
@@ -3797,28 +3797,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -3868,28 +3868,28 @@
         <v>0.3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
@@ -3933,28 +3933,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.1</v>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1.22</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>13.81</v>
+        <v>13.51</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9.68</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>7.86</v>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>3.97</v>
@@ -4103,19 +4103,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>24.83</v>
+        <v>24.7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>21.4</v>
+        <v>21.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>20.46</v>
+        <v>20.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>16.97</v>
+        <v>16.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7.96</v>
+        <v>7.93</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>3.83</v>
@@ -4137,16 +4137,16 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>24.65</v>
+        <v>24.24</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>22.33</v>
+        <v>22.15</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20.56</v>
+        <v>20.45</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15.83</v>
+        <v>15.73</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>4.97</v>
@@ -4171,16 +4171,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16.94</v>
+        <v>16.7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13.37</v>
+        <v>13.24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12.43</v>
+        <v>12.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11.02</v>
+        <v>10.85</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>4.03</v>
@@ -4205,28 +4205,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.03</v>
+        <v>4.79</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.28</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1.21</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>13.12</v>
+        <v>12.4</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>8.58</v>
@@ -4384,22 +4384,22 @@
         <v>7.5</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
@@ -4409,28 +4409,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>16.1</v>
+        <v>15.62</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12.57</v>
+        <v>12.37</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>11.63</v>
+        <v>11.42</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.71</v>
@@ -4443,31 +4443,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.12</v>
+        <v>7.01</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>5.14</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H27" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="J27" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -4477,28 +4477,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>7.09</v>
+        <v>7.06</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.71</v>
@@ -4511,19 +4511,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>16.1</v>
+        <v>16.03</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.94</v>
+        <v>13.84</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.96</v>
+        <v>11.9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>2.62</v>
@@ -4545,31 +4545,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>44.41</v>
+        <v>43.82</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>33.61</v>
+        <v>33.33</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>30.35</v>
+        <v>30.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>26.7</v>
+        <v>26.53</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>11.04</v>
+        <v>10.97</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31">
@@ -4579,28 +4579,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>36.66</v>
+        <v>36.32</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>31.69</v>
+        <v>31.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30.88</v>
+        <v>30.68</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>28.19</v>
+        <v>27.99</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12.1</v>
+        <v>12.03</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>1.81</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>16.49</v>
+        <v>16.25</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>13.47</v>
+        <v>13.23</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>13.23</v>
+        <v>12.99</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12.47</v>
+        <v>12.22</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>7.05</v>
+        <v>6.88</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>2.78</v>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1.95</v>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1.75</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.63</v>
+        <v>6.39</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>3.26</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>4.94</v>
+        <v>4.23</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2.52</v>
@@ -4919,19 +4919,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>30.65</v>
+        <v>30.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.05</v>
+        <v>26.98</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>24.53</v>
+        <v>24.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22.65</v>
+        <v>22.61</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.86</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>10.42</v>
@@ -4953,16 +4953,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>28.4</v>
+        <v>28.09</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>24.03</v>
+        <v>23.92</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>21.81</v>
+        <v>21.77</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>20.28</v>
+        <v>20.24</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>17.64</v>
@@ -4987,19 +4987,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>12.97</v>
+        <v>12.87</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>9.74</v>
+        <v>9.68</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>7.63</v>
+        <v>7.56</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>5.01</v>
@@ -5021,25 +5021,25 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24.03</v>
+        <v>23.68</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>16.84</v>
+        <v>16.6</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>15</v>
+        <v>14.76</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>13.47</v>
+        <v>13.26</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.35</v>
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>37.47</v>
+        <v>37.03</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>24.4</v>
+        <v>23.99</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>16.36</v>
+        <v>16.16</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.54</v>
+        <v>13.37</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.59</v>
+        <v>7.46</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>2.42</v>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>9.98</v>
+        <v>9.81</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>7.12</v>
+        <v>6.99</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>5.24</v>
+        <v>5.14</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.44</v>
@@ -5123,19 +5123,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>9.49</v>
+        <v>9.41</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>6.55</v>
+        <v>6.51</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.82</v>
@@ -5157,19 +5157,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.39</v>
+        <v>15.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.62</v>
+        <v>10.58</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.06</v>
+        <v>7.02</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -5191,19 +5191,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>27.05</v>
+        <v>26.84</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>23.47</v>
+        <v>23.44</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>20.9</v>
+        <v>20.87</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>16.49</v>
+        <v>16.42</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>3.72</v>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>24.7</v>
+        <v>24.53</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>15.42</v>
+        <v>15.39</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>9.140000000000001</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>18.4</v>
+        <v>18.19</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>15.03</v>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.75</v>
+        <v>35.55</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>30.71</v>
@@ -5327,19 +5327,19 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>67.78</v>
+        <v>67.37</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>62.03</v>
+        <v>61.79</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>59.78</v>
+        <v>59.64</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>47.82</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>39.75</v>
+        <v>39.78</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>4.67</v>
@@ -5361,19 +5361,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>79.86</v>
+        <v>79.31</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>73.84999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>71.98</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46.7</v>
+        <v>46.49</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46.25</v>
+        <v>46.04</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>10.69</v>
@@ -5395,19 +5395,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>81.45</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>75.84</v>
+        <v>75.13</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>71.81</v>
+        <v>71.17</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>47.08</v>
+        <v>46.67</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>7.63</v>
@@ -5416,7 +5416,7 @@
         <v>0.37</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="J55" s="3" t="n">
         <v>0</v>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>37.78</v>
+        <v>37.53</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>30.52</v>
+        <v>30.31</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>28.02</v>
+        <v>27.85</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -5463,16 +5463,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>34.38</v>
+        <v>34.07</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>27.45</v>
+        <v>27.18</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>24.73</v>
+        <v>24.46</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>12.87</v>
+        <v>12.77</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>9.27</v>
@@ -5497,19 +5497,19 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>8.4</v>
+        <v>8.27</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -5531,16 +5531,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>12.75</v>
+        <v>12.61</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.97</v>
+        <v>7.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0.65</v>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>21.34</v>
+        <v>21.14</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>16.1</v>
+        <v>15.96</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>13.58</v>
+        <v>13.44</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>2.02</v>
@@ -5599,16 +5599,16 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>33.06</v>
+        <v>32.74</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>30.21</v>
+        <v>29.93</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>26.25</v>
+        <v>26.11</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>7.22</v>
@@ -5633,19 +5633,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>42.88</v>
+        <v>42.57</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>33.67</v>
+        <v>33.53</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>23.02</v>
+        <v>22.92</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>17.78</v>
+        <v>17.71</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>3.73</v>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>33.5</v>
+        <v>33.53</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>30.31</v>
+        <v>30.38</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>19.49</v>
@@ -5735,19 +5735,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>51.28</v>
+        <v>50.91</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>47.88</v>
+        <v>47.51</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>38.17</v>
+        <v>38.1</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>35.22</v>
+        <v>35.15</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.51</v>
+        <v>21.47</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>4.3</v>
@@ -5769,19 +5769,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>83.68000000000001</v>
+        <v>83.16</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>81.67</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>76.84</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>73.23</v>
+        <v>72.92</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.37</v>
+        <v>54.24</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>4.2</v>
@@ -5803,19 +5803,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>77.52</v>
+        <v>76.88</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>76.31</v>
+        <v>75.67</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>71.27</v>
+        <v>70.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>37.74</v>
+        <v>37.43</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>1.98</v>
@@ -5837,19 +5837,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>38.19</v>
+        <v>38.06</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>37.26</v>
+        <v>37.15</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>33.23</v>
+        <v>33.19</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>27.05</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>36.83</v>
+        <v>36.59</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>35.62</v>
+        <v>35.38</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>27.79</v>
+        <v>27.59</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>2.28</v>
@@ -5905,16 +5905,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>47.58</v>
+        <v>47.21</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>46.54</v>
+        <v>46.2</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>44.89</v>
+        <v>44.56</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>30.38</v>
+        <v>30.21</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0.1</v>
@@ -5939,16 +5939,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>47.02</v>
+        <v>46.43</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>46.06</v>
+        <v>45.68</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>43.3</v>
+        <v>43.01</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>15.77</v>
+        <v>15.74</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>1.15</v>
@@ -5973,16 +5973,16 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>35.75</v>
+        <v>35.28</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>31.05</v>
+        <v>30.75</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>45.35</v>
+        <v>44.58</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>41.18</v>
+        <v>40.8</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.94</v>
+        <v>31.87</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>2.99</v>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>25.2</v>
+        <v>24.87</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>22.65</v>
+        <v>22.58</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>9.880000000000001</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>33.96</v>
+        <v>33.72</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>31.46</v>
+        <v>31.39</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>14.24</v>
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>43.85</v>
+        <v>43.75</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>11.53</v>
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>70.5</v>
+        <v>70.13</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>26.81</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>88.65000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>33.54</v>
+        <v>33.51</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>17.92</v>
+        <v>17.88</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>3.78</v>
@@ -6211,16 +6211,16 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>77.89</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.26000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>1.92</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>71.84</v>
+        <v>71.08</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>55.52</v>
+        <v>55.07</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>4.06</v>
@@ -6279,13 +6279,13 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>59.58</v>
+        <v>57.73</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>25.74</v>
+        <v>25.4</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>3.49</v>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>25.3</v>
+        <v>21.37</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0.1</v>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>19.64</v>
+        <v>19.12</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>1.53</v>
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>24.23</v>
+        <v>23.86</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>2.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>39.06</v>
+        <v>38.61</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>1.98</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.65</v>
+        <v>18.48</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0.17</v>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.48</v>
+        <v>22.38</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0</v>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>34.27</v>
+        <v>34.04</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0.84</v>
@@ -6780,7 +6780,7 @@
         <v>2976</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>3</v>
@@ -6854,7 +6854,7 @@
         <v>2976</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>31</v>
@@ -6891,7 +6891,7 @@
         <v>2976</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>195</v>
@@ -6928,28 +6928,28 @@
         <v>2880</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>85</v>
@@ -6965,31 +6965,31 @@
         <v>2976</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -7002,28 +7002,28 @@
         <v>2880</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>2</v>
@@ -7079,28 +7079,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7113,7 +7113,7 @@
         <v>2784</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -7150,28 +7150,28 @@
         <v>2976</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>3</v>
@@ -7187,7 +7187,7 @@
         <v>2880</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>35</v>
@@ -7224,13 +7224,13 @@
         <v>2976</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>234</v>
@@ -7298,7 +7298,7 @@
         <v>2976</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>118</v>
@@ -7335,19 +7335,19 @@
         <v>2976</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>114</v>
@@ -7372,16 +7372,16 @@
         <v>2880</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>143</v>
@@ -7409,16 +7409,16 @@
         <v>2976</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>120</v>
@@ -7446,28 +7446,28 @@
         <v>2880</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>8</v>
@@ -7594,7 +7594,7 @@
         <v>2976</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>36</v>
@@ -7631,7 +7631,7 @@
         <v>2880</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>247</v>
@@ -7640,22 +7640,22 @@
         <v>216</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -7668,28 +7668,28 @@
         <v>2976</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>21</v>
@@ -7705,31 +7705,31 @@
         <v>2880</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>148</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I27" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>41</v>
-      </c>
       <c r="K27" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -7742,28 +7742,28 @@
         <v>2976</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>21</v>
@@ -7779,19 +7779,19 @@
         <v>2976</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>78</v>
@@ -7816,31 +7816,31 @@
         <v>2880</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1279</v>
+        <v>1262</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -7853,28 +7853,28 @@
         <v>2976</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>54</v>
@@ -7890,22 +7890,22 @@
         <v>2880</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>80</v>
@@ -7927,10 +7927,10 @@
         <v>2976</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>58</v>
@@ -8001,10 +8001,10 @@
         <v>2688</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>47</v>
@@ -8038,7 +8038,7 @@
         <v>2976</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>24</v>
@@ -8149,7 +8149,7 @@
         <v>2880</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>94</v>
@@ -8186,7 +8186,7 @@
         <v>2976</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>75</v>
@@ -8223,19 +8223,19 @@
         <v>2976</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>310</v>
@@ -8260,16 +8260,16 @@
         <v>2880</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>508</v>
@@ -8297,19 +8297,19 @@
         <v>2976</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>149</v>
@@ -8334,25 +8334,25 @@
         <v>2880</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>10</v>
@@ -8371,22 +8371,22 @@
         <v>2976</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>72</v>
@@ -8408,22 +8408,22 @@
         <v>2976</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>13</v>
@@ -8445,19 +8445,19 @@
         <v>2688</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>22</v>
@@ -8482,19 +8482,19 @@
         <v>2976</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>28</v>
@@ -8519,19 +8519,19 @@
         <v>2880</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>107</v>
@@ -8556,13 +8556,13 @@
         <v>2976</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>272</v>
@@ -8593,7 +8593,7 @@
         <v>2880</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>433</v>
@@ -8630,7 +8630,7 @@
         <v>2976</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>914</v>
@@ -8667,19 +8667,19 @@
         <v>2976</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>1423</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>139</v>
@@ -8704,19 +8704,19 @@
         <v>2880</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>2300</v>
+        <v>2284</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2127</v>
+        <v>2113</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2086</v>
+        <v>2073</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>308</v>
@@ -8741,19 +8741,19 @@
         <v>2976</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>2424</v>
+        <v>2400</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2257</v>
+        <v>2236</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2137</v>
+        <v>2118</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1494</v>
+        <v>1479</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>1401</v>
+        <v>1389</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>227</v>
@@ -8762,7 +8762,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
@@ -8778,19 +8778,19 @@
         <v>2880</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
@@ -8815,16 +8815,16 @@
         <v>2976</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G57" s="6" t="n">
         <v>276</v>
@@ -8852,19 +8852,19 @@
         <v>2976</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
@@ -8889,16 +8889,16 @@
         <v>2784</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>18</v>
@@ -8926,13 +8926,13 @@
         <v>2976</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>60</v>
@@ -8963,16 +8963,16 @@
         <v>2880</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>208</v>
@@ -9000,19 +9000,19 @@
         <v>2976</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>1363</v>
+        <v>1354</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>111</v>
@@ -9074,10 +9074,10 @@
         <v>2976</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>580</v>
@@ -9111,19 +9111,19 @@
         <v>2976</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1526</v>
+        <v>1515</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1425</v>
+        <v>1414</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>128</v>
@@ -9148,19 +9148,19 @@
         <v>2880</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>2410</v>
+        <v>2395</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2352</v>
+        <v>2334</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2213</v>
+        <v>2202</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>2109</v>
+        <v>2100</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>121</v>
@@ -9185,19 +9185,19 @@
         <v>2976</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2307</v>
+        <v>2288</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2271</v>
+        <v>2252</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2121</v>
+        <v>2108</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1957</v>
+        <v>1942</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>59</v>
@@ -9222,19 +9222,19 @@
         <v>2880</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>779</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>9</v>
@@ -9259,16 +9259,16 @@
         <v>2976</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>68</v>
@@ -9296,16 +9296,16 @@
         <v>2976</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>1416</v>
+        <v>1405</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1385</v>
+        <v>1375</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1336</v>
+        <v>1326</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>3</v>
@@ -9333,16 +9333,16 @@
         <v>2688</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1238</v>
+        <v>1228</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G71" s="6" t="n">
         <v>31</v>
@@ -9370,16 +9370,16 @@
         <v>2976</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -9407,13 +9407,13 @@
         <v>2880</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1306</v>
+        <v>1284</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1186</v>
+        <v>1175</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>86</v>
@@ -9444,10 +9444,10 @@
         <v>2976</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>294</v>
@@ -9481,10 +9481,10 @@
         <v>2880</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>410</v>
@@ -9518,10 +9518,10 @@
         <v>2976</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>1503</v>
+        <v>1494</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>343</v>
@@ -9555,10 +9555,10 @@
         <v>2976</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>2098</v>
+        <v>2087</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>798</v>
@@ -9592,16 +9592,16 @@
         <v>2880</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>2553</v>
+        <v>2537</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>2434</v>
+        <v>2416</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>109</v>
@@ -9629,16 +9629,16 @@
         <v>2976</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>2318</v>
+        <v>2297</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>2091</v>
+        <v>2077</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>57</v>
@@ -9666,13 +9666,13 @@
         <v>2880</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2069</v>
+        <v>2047</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>117</v>
@@ -9703,13 +9703,13 @@
         <v>2976</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>1773</v>
+        <v>1718</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>104</v>
@@ -9740,10 +9740,10 @@
         <v>2976</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>753</v>
+        <v>636</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>3</v>
@@ -9777,7 +9777,7 @@
         <v>2688</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>41</v>
@@ -9814,13 +9814,13 @@
         <v>2976</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>71</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>2</v>
@@ -9851,7 +9851,7 @@
         <v>2880</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>57</v>
@@ -9888,7 +9888,7 @@
         <v>2976</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>5</v>
@@ -9962,7 +9962,7 @@
         <v>2976</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>0</v>
@@ -9999,7 +9999,7 @@
         <v>2976</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>25</v>

--- a/outputs/QLD_negative_prices.xlsx
+++ b/outputs/QLD_negative_prices.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -74,7 +76,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6579,108 +6581,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B89">
+  <conditionalFormatting sqref="B2:J89">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C89">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D89">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E89">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F89">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G89">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H89">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I89">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J89">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="num" val="50"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
